--- a/examples/results/Tryptophan_design_results_ecFactory_level_2_result.xlsx
+++ b/examples/results/Tryptophan_design_results_ecFactory_level_2_result.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gene_name</t>
@@ -461,7 +466,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b4467</t>
         </is>
@@ -479,14 +484,14 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.908976254592349e-17</v>
+        <v>-2.179974776010317e-15</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>b4468</t>
         </is>
@@ -504,14 +509,14 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>4.503629712599597e-14</v>
+        <v>2.770549763790643e-13</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.115036088105764e-05</v>
+        <v>-9.313539209499633e-05</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>b2979</t>
         </is>
@@ -529,39 +534,39 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3.616776336851162e-15</v>
+        <v>2.814149259358164e-14</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.115036097964629e-05</v>
+        <v>-9.313539254815938e-05</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>b4025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1000</v>
+        <v>0.1824571256088911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>3.82486483842342e-14</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>b2097</t>
         </is>
@@ -579,14 +584,14 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>b2296</t>
         </is>
@@ -604,14 +609,14 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.585436202455304e-15</v>
+        <v>-3.567231455524434e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>b3709</t>
         </is>
@@ -634,7 +639,7 @@
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>b3161</t>
         </is>
@@ -657,7 +662,7 @@
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>b0112</t>
         </is>
@@ -680,7 +685,7 @@
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>b1723</t>
         </is>
@@ -698,14 +703,14 @@
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2.108828328790861e-12</v>
+        <v>8.736744373155259e-12</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>b3708</t>
         </is>
@@ -723,14 +728,14 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.034497122102086e-13</v>
+        <v>3.805046885892729e-14</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>b1264</t>
         </is>
@@ -748,14 +753,14 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>b1260</t>
         </is>
@@ -773,14 +778,14 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.05658377824727687</v>
+        <v>-0.05649804552444944</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>b1262</t>
         </is>
@@ -798,14 +803,14 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>b1263</t>
         </is>
@@ -823,14 +828,14 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.25</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>b1261</t>
         </is>
@@ -848,14 +853,14 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05658368941756006</v>
+        <v>-0.05659603213146488</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>b1693</t>
         </is>
@@ -873,14 +878,14 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.25</v>
+        <v>1.248531009433552e-14</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>b3389</t>
         </is>
@@ -898,14 +903,14 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.25</v>
+        <v>9.908976265345648e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>b2329</t>
         </is>
@@ -923,14 +928,14 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.25</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>b0908</t>
         </is>
@@ -948,14 +953,14 @@
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.086646106655169e-14</v>
+        <v>3.491923235907807e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>b3281</t>
         </is>
@@ -973,14 +978,14 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.437792456101654e-13</v>
+        <v>1.961977300538439e-14</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.002456747357808343</v>
+        <v>0.00246637325015703</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>b0754</t>
         </is>
@@ -998,14 +1003,14 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.25</v>
+        <v>-5.94538575920739e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>b0388</t>
         </is>
@@ -1023,14 +1028,14 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.25</v>
+        <v>8.323540062890345e-15</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>b4094</t>
         </is>
@@ -1048,14 +1053,14 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.449936945940107e-16</v>
+        <v>2.885493888468653e-13</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1964705108954162</v>
+        <v>0.196798132308395</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>b4383</t>
         </is>
@@ -1073,14 +1078,14 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>4.954488132672824e-17</v>
+        <v>1.98179525306913e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.01221514615465938</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>b3870</t>
         </is>
@@ -1098,14 +1103,14 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.753335914486308e-13</v>
+        <v>1.330379153385307e-12</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>b2417</t>
         </is>
@@ -1123,14 +1128,14 @@
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.09873563999123627</v>
+        <v>-0.3949425599649451</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2418714099521334</v>
+        <v>-0.9674856398085334</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>b1101</t>
         </is>
@@ -1148,14 +1153,14 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.07528620790610717</v>
+        <v>-0.3011448316241171</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.244305074792047</v>
+        <v>-0.9772202991682226</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>b2744</t>
         </is>
@@ -1173,14 +1178,14 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.624150633383566e-14</v>
+        <v>4.597764987120381e-14</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.004508877205350624</v>
+        <v>-0.004518503097356697</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>b0728</t>
         </is>
@@ -1198,14 +1203,14 @@
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>4.409494438078813e-15</v>
+        <v>1.98179525306913e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.04558452623620536</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>b0729</t>
         </is>
@@ -1223,14 +1228,14 @@
         <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>8.34831250355371e-14</v>
+        <v>1.028551736342878e-13</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.04558452623632846</v>
+        <v>-0.04581675721038668</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>b3919</t>
         </is>
@@ -1248,14 +1253,14 @@
         <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>5.459845922205453e-14</v>
+        <v>2.158175030592282e-13</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.005302093262610551</v>
+        <v>-0.005311719155056809</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>b0451</t>
         </is>
@@ -1278,7 +1283,7 @@
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>b0875</t>
         </is>
@@ -1301,7 +1306,7 @@
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>b3875</t>
         </is>
@@ -1324,7 +1329,7 @@
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>b1319</t>
         </is>
@@ -1347,7 +1352,7 @@
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>b0957</t>
         </is>
@@ -1370,7 +1375,7 @@
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>b2551</t>
         </is>
@@ -1388,14 +1393,14 @@
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.341744809821215e-15</v>
+        <v>2.001613205599821e-14</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>b0529</t>
         </is>
@@ -1413,14 +1418,14 @@
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>-8.948796465233656e-13</v>
+        <v>1.240603828421275e-13</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>b1852</t>
         </is>
@@ -1438,14 +1443,14 @@
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>5.202212539306466e-15</v>
+        <v>-7.927181012276519e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>b0767</t>
         </is>
@@ -1463,39 +1468,39 @@
         <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.2500000000000001</v>
+        <v>8.820970671410697e-13</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>b2029</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.1824571256088911</v>
+        <v>1000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2438761579269342</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>b2906</t>
         </is>
@@ -1513,14 +1518,14 @@
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7498940131581511</v>
+        <v>0.9999999999999957</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>b3867</t>
         </is>
@@ -1538,14 +1543,14 @@
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>3.765410980831347e-15</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>b3125</t>
         </is>
@@ -1563,14 +1568,14 @@
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.93702056504845e-13</v>
+        <v>-1.298868608861508e-12</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>b1033</t>
         </is>
@@ -1588,14 +1593,14 @@
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>b0508</t>
         </is>
@@ -1613,14 +1618,14 @@
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>9.215347926771453e-15</v>
+        <v>-3.408687835278903e-14</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>b0509</t>
         </is>
@@ -1638,14 +1643,14 @@
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>b3553</t>
         </is>
@@ -1663,14 +1668,14 @@
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>8.120406049450759e-14</v>
+        <v>1.288166914494934e-14</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.25</v>
+        <v>-0.05034215391138917</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>b1199</t>
         </is>
@@ -1688,14 +1693,14 @@
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>4.984215061468861e-14</v>
+        <v>1.93938483465345e-12</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1160803467940846</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>b1200</t>
         </is>
@@ -1713,14 +1718,14 @@
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>3.864500743484803e-15</v>
+        <v>3.96359050613826e-16</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.1160803467939918</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>b3946</t>
         </is>
@@ -1738,14 +1743,14 @@
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>4.850443881886695e-14</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>b1198</t>
         </is>
@@ -1763,14 +1768,14 @@
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.506164392332539e-14</v>
+        <v>1.583454407202235e-13</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.1160803467940041</v>
+        <v>-0.04187215185690053</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>b0825</t>
         </is>
@@ -1788,14 +1793,14 @@
         <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>8.224945749050156e-13</v>
+        <v>3.099725955325426e-12</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>b1473</t>
         </is>
